--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD2"/>
+  <dimension ref="A1:AD3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -666,6 +666,101 @@
       <c r="AD2" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>15:09:16</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8276</v>
+      </c>
+      <c r="F3" t="n">
+        <v>39786</v>
+      </c>
+      <c r="G3" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.626</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3214</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>3580</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>59570</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>36643</v>
+      </c>
+      <c r="R3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>14861</v>
+      </c>
+      <c r="T3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>5559</v>
+      </c>
+      <c r="V3" t="n">
+        <v>50.2</v>
+      </c>
+      <c r="X3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD3"/>
+  <dimension ref="A1:AD4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -759,6 +759,101 @@
         </is>
       </c>
       <c r="AD3" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>15:10:21</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8273</v>
+      </c>
+      <c r="F4" t="n">
+        <v>39845</v>
+      </c>
+      <c r="G4" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.692</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3459</v>
+      </c>
+      <c r="K4" t="n">
+        <v>245</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>2201</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-1379</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>60246</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>35598</v>
+      </c>
+      <c r="R4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>14849</v>
+      </c>
+      <c r="T4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>5558</v>
+      </c>
+      <c r="V4" t="n">
+        <v>50</v>
+      </c>
+      <c r="X4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>⚠ Conflict</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD4"/>
+  <dimension ref="A1:AD5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -856,6 +856,101 @@
       <c r="AD4" t="inlineStr">
         <is>
           <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>15:11:27</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8283</v>
+      </c>
+      <c r="F5" t="n">
+        <v>39941</v>
+      </c>
+      <c r="G5" t="n">
+        <v>11.53</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.644</v>
+      </c>
+      <c r="I5" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3342</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-117</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>3655</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1454</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>60061</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>36535</v>
+      </c>
+      <c r="R5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>14870</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5558</v>
+      </c>
+      <c r="V5" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="X5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD5"/>
+  <dimension ref="A1:AD6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -949,6 +949,101 @@
         </is>
       </c>
       <c r="AD5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>15:12:32</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8279</v>
+      </c>
+      <c r="F6" t="n">
+        <v>39957</v>
+      </c>
+      <c r="G6" t="n">
+        <v>11.57</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.646</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3363</v>
+      </c>
+      <c r="K6" t="n">
+        <v>21</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>3689</v>
+      </c>
+      <c r="N6" t="n">
+        <v>34</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>60307</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>36636</v>
+      </c>
+      <c r="R6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>14911</v>
+      </c>
+      <c r="T6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5558</v>
+      </c>
+      <c r="V6" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD6"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1046,6 +1046,101 @@
       <c r="AD6" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>15:13:36</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8274</v>
+      </c>
+      <c r="F7" t="n">
+        <v>39928</v>
+      </c>
+      <c r="G7" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.709</v>
+      </c>
+      <c r="I7" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3542</v>
+      </c>
+      <c r="K7" t="n">
+        <v>179</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>2265</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-1424</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>60999</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>35685</v>
+      </c>
+      <c r="R7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>14940</v>
+      </c>
+      <c r="T7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U7" t="n">
+        <v>5556</v>
+      </c>
+      <c r="V7" t="n">
+        <v>50</v>
+      </c>
+      <c r="X7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1139,6 +1139,101 @@
         </is>
       </c>
       <c r="AD7" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>15:14:43</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8268</v>
+      </c>
+      <c r="F8" t="n">
+        <v>39928</v>
+      </c>
+      <c r="G8" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.711</v>
+      </c>
+      <c r="I8" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3593</v>
+      </c>
+      <c r="K8" t="n">
+        <v>51</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>2257</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-8</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>61108</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>35707</v>
+      </c>
+      <c r="R8" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>14958</v>
+      </c>
+      <c r="T8" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5557</v>
+      </c>
+      <c r="V8" t="n">
+        <v>50</v>
+      </c>
+      <c r="X8" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>⚠ Conflict</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD8"/>
+  <dimension ref="A1:AD9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1234,6 +1234,101 @@
         </is>
       </c>
       <c r="AD8" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>15:15:48</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8268</v>
+      </c>
+      <c r="F9" t="n">
+        <v>39949</v>
+      </c>
+      <c r="G9" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.706</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3705</v>
+      </c>
+      <c r="K9" t="n">
+        <v>112</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>2268</v>
+      </c>
+      <c r="N9" t="n">
+        <v>11</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>61367</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>35974</v>
+      </c>
+      <c r="R9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>14984</v>
+      </c>
+      <c r="T9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5554</v>
+      </c>
+      <c r="V9" t="n">
+        <v>50</v>
+      </c>
+      <c r="X9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>⚠ Conflict</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD9"/>
+  <dimension ref="A1:AD10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1329,6 +1329,101 @@
         </is>
       </c>
       <c r="AD9" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>15:16:53</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8277</v>
+      </c>
+      <c r="F10" t="n">
+        <v>40013</v>
+      </c>
+      <c r="G10" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.669</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3498</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-207</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>3750</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1482</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>61387</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>36788</v>
+      </c>
+      <c r="R10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15139</v>
+      </c>
+      <c r="T10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5554</v>
+      </c>
+      <c r="V10" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="X10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>⚠ Conflict</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1426,6 +1426,101 @@
       <c r="AD10" t="inlineStr">
         <is>
           <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>15:17:59</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8280</v>
+      </c>
+      <c r="F11" t="n">
+        <v>40134</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.677</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3632</v>
+      </c>
+      <c r="K11" t="n">
+        <v>134</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>3722</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-28</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>61904</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>36903</v>
+      </c>
+      <c r="R11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15190</v>
+      </c>
+      <c r="T11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U11" t="n">
+        <v>5574</v>
+      </c>
+      <c r="V11" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1521,6 +1521,101 @@
       <c r="AD11" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>15:19:04</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8287</v>
+      </c>
+      <c r="F12" t="n">
+        <v>40197</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.689</v>
+      </c>
+      <c r="I12" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3749</v>
+      </c>
+      <c r="K12" t="n">
+        <v>117</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>3701</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-21</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>62179</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>36820</v>
+      </c>
+      <c r="R12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15259</v>
+      </c>
+      <c r="T12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U12" t="n">
+        <v>5579</v>
+      </c>
+      <c r="V12" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="X12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1614,6 +1614,101 @@
         </is>
       </c>
       <c r="AD12" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>15:20:10</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8296</v>
+      </c>
+      <c r="F13" t="n">
+        <v>40223</v>
+      </c>
+      <c r="G13" t="n">
+        <v>12.32</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.698</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3890</v>
+      </c>
+      <c r="K13" t="n">
+        <v>141</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>3754</v>
+      </c>
+      <c r="N13" t="n">
+        <v>53</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>62572</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>36842</v>
+      </c>
+      <c r="R13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15300</v>
+      </c>
+      <c r="T13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U13" t="n">
+        <v>5565</v>
+      </c>
+      <c r="V13" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="X13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:AD14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,6 +1709,101 @@
         </is>
       </c>
       <c r="AD13" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>15:21:15</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8296</v>
+      </c>
+      <c r="F14" t="n">
+        <v>40390</v>
+      </c>
+      <c r="G14" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.702</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3945</v>
+      </c>
+      <c r="K14" t="n">
+        <v>55</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>3672</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-82</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>62843</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>36931</v>
+      </c>
+      <c r="R14" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15322</v>
+      </c>
+      <c r="T14" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5568</v>
+      </c>
+      <c r="V14" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="X14" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD14"/>
+  <dimension ref="A1:AD15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1804,6 +1804,101 @@
         </is>
       </c>
       <c r="AD14" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>15:22:20</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="E15" t="n">
+        <v>8306</v>
+      </c>
+      <c r="F15" t="n">
+        <v>40389</v>
+      </c>
+      <c r="G15" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.706</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3892</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-53</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>3800</v>
+      </c>
+      <c r="N15" t="n">
+        <v>128</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>63290</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>37105</v>
+      </c>
+      <c r="R15" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15491</v>
+      </c>
+      <c r="T15" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5566</v>
+      </c>
+      <c r="V15" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="X15" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD15"/>
+  <dimension ref="A1:AD16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1899,6 +1899,101 @@
         </is>
       </c>
       <c r="AD15" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15:23:27</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E16" t="n">
+        <v>8311</v>
+      </c>
+      <c r="F16" t="n">
+        <v>40397</v>
+      </c>
+      <c r="G16" t="n">
+        <v>12.8</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.705</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3952</v>
+      </c>
+      <c r="K16" t="n">
+        <v>60</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>3966</v>
+      </c>
+      <c r="N16" t="n">
+        <v>166</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>63690</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>37357</v>
+      </c>
+      <c r="R16" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15593</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U16" t="n">
+        <v>5573</v>
+      </c>
+      <c r="V16" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD16"/>
+  <dimension ref="A1:AD17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1994,6 +1994,101 @@
         </is>
       </c>
       <c r="AD16" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>15:24:35</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8308</v>
+      </c>
+      <c r="F17" t="n">
+        <v>40419</v>
+      </c>
+      <c r="G17" t="n">
+        <v>12.86</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.709</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4130</v>
+      </c>
+      <c r="K17" t="n">
+        <v>178</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>4071</v>
+      </c>
+      <c r="N17" t="n">
+        <v>105</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>64158</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>37540</v>
+      </c>
+      <c r="R17" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15606</v>
+      </c>
+      <c r="T17" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U17" t="n">
+        <v>5582</v>
+      </c>
+      <c r="V17" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="X17" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD17"/>
+  <dimension ref="A1:AD18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2089,6 +2089,101 @@
         </is>
       </c>
       <c r="AD17" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>15:25:41</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8313</v>
+      </c>
+      <c r="F18" t="n">
+        <v>40459</v>
+      </c>
+      <c r="G18" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.721</v>
+      </c>
+      <c r="I18" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4224</v>
+      </c>
+      <c r="K18" t="n">
+        <v>94</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>4105</v>
+      </c>
+      <c r="N18" t="n">
+        <v>34</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>64802</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>37658</v>
+      </c>
+      <c r="R18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15778</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U18" t="n">
+        <v>5587</v>
+      </c>
+      <c r="V18" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="X18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD18"/>
+  <dimension ref="A1:AD19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2184,6 +2184,101 @@
         </is>
       </c>
       <c r="AD18" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>15:26:46</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8313</v>
+      </c>
+      <c r="F19" t="n">
+        <v>40561</v>
+      </c>
+      <c r="G19" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I19" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4443</v>
+      </c>
+      <c r="K19" t="n">
+        <v>219</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>4235</v>
+      </c>
+      <c r="N19" t="n">
+        <v>130</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>65478</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>37853</v>
+      </c>
+      <c r="R19" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>16052</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U19" t="n">
+        <v>5588</v>
+      </c>
+      <c r="V19" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="X19" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:AD20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2279,6 +2279,101 @@
         </is>
       </c>
       <c r="AD19" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>15:27:52</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8315</v>
+      </c>
+      <c r="F20" t="n">
+        <v>40608</v>
+      </c>
+      <c r="G20" t="n">
+        <v>13.39</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.731</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4476</v>
+      </c>
+      <c r="K20" t="n">
+        <v>33</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>4236</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>65720</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>37968</v>
+      </c>
+      <c r="R20" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>16117</v>
+      </c>
+      <c r="T20" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U20" t="n">
+        <v>5598</v>
+      </c>
+      <c r="V20" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="X20" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD20"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2374,6 +2374,101 @@
         </is>
       </c>
       <c r="AD20" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>15:28:57</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8317</v>
+      </c>
+      <c r="F21" t="n">
+        <v>40723</v>
+      </c>
+      <c r="G21" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.738</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4709</v>
+      </c>
+      <c r="K21" t="n">
+        <v>233</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>4277</v>
+      </c>
+      <c r="N21" t="n">
+        <v>41</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>66231</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>38097</v>
+      </c>
+      <c r="R21" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>16234</v>
+      </c>
+      <c r="T21" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U21" t="n">
+        <v>5599</v>
+      </c>
+      <c r="V21" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD21"/>
+  <dimension ref="A1:AD22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2469,6 +2469,101 @@
         </is>
       </c>
       <c r="AD21" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>15:30:02</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E22" t="n">
+        <v>8317</v>
+      </c>
+      <c r="F22" t="n">
+        <v>40882</v>
+      </c>
+      <c r="G22" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.753</v>
+      </c>
+      <c r="I22" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J22" t="n">
+        <v>4800</v>
+      </c>
+      <c r="K22" t="n">
+        <v>91</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>4116</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-161</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>66662</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>38032</v>
+      </c>
+      <c r="R22" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>16376</v>
+      </c>
+      <c r="T22" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U22" t="n">
+        <v>5618</v>
+      </c>
+      <c r="V22" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="X22" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2564,6 +2564,101 @@
         </is>
       </c>
       <c r="AD22" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>15:31:08</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E23" t="n">
+        <v>8317</v>
+      </c>
+      <c r="F23" t="n">
+        <v>40904</v>
+      </c>
+      <c r="G23" t="n">
+        <v>14.22</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.757</v>
+      </c>
+      <c r="I23" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5027</v>
+      </c>
+      <c r="K23" t="n">
+        <v>227</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>4161</v>
+      </c>
+      <c r="N23" t="n">
+        <v>45</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>67236</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>38260</v>
+      </c>
+      <c r="R23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>16554</v>
+      </c>
+      <c r="T23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U23" t="n">
+        <v>5584</v>
+      </c>
+      <c r="V23" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="X23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD23"/>
+  <dimension ref="A1:AD24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2659,6 +2659,101 @@
         </is>
       </c>
       <c r="AD23" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>15:32:14</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8303</v>
+      </c>
+      <c r="F24" t="n">
+        <v>40915</v>
+      </c>
+      <c r="G24" t="n">
+        <v>14.25</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.761</v>
+      </c>
+      <c r="I24" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J24" t="n">
+        <v>5167</v>
+      </c>
+      <c r="K24" t="n">
+        <v>140</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>4294</v>
+      </c>
+      <c r="N24" t="n">
+        <v>133</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>67599</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>38385</v>
+      </c>
+      <c r="R24" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>16563</v>
+      </c>
+      <c r="T24" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U24" t="n">
+        <v>5611</v>
+      </c>
+      <c r="V24" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="X24" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD24"/>
+  <dimension ref="A1:AD25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2754,6 +2754,101 @@
         </is>
       </c>
       <c r="AD24" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>15:33:19</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8298</v>
+      </c>
+      <c r="F25" t="n">
+        <v>40896</v>
+      </c>
+      <c r="G25" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.777</v>
+      </c>
+      <c r="I25" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J25" t="n">
+        <v>5381</v>
+      </c>
+      <c r="K25" t="n">
+        <v>214</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>4201</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-93</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>68147</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>38359</v>
+      </c>
+      <c r="R25" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S25" t="n">
+        <v>16644</v>
+      </c>
+      <c r="T25" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5597</v>
+      </c>
+      <c r="V25" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="X25" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD25"/>
+  <dimension ref="A1:AD26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2851,6 +2851,101 @@
       <c r="AD25" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>15:34:23</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="E26" t="n">
+        <v>8295</v>
+      </c>
+      <c r="F26" t="n">
+        <v>40701</v>
+      </c>
+      <c r="G26" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I26" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5583</v>
+      </c>
+      <c r="K26" t="n">
+        <v>202</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>4272</v>
+      </c>
+      <c r="N26" t="n">
+        <v>71</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>68425</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>38652</v>
+      </c>
+      <c r="R26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S26" t="n">
+        <v>16491</v>
+      </c>
+      <c r="T26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U26" t="n">
+        <v>5644</v>
+      </c>
+      <c r="V26" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="X26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD26"/>
+  <dimension ref="A1:AD27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2944,6 +2944,101 @@
         </is>
       </c>
       <c r="AD26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>15:35:28</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="E27" t="n">
+        <v>8295</v>
+      </c>
+      <c r="F27" t="n">
+        <v>40785</v>
+      </c>
+      <c r="G27" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.771</v>
+      </c>
+      <c r="I27" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J27" t="n">
+        <v>5825</v>
+      </c>
+      <c r="K27" t="n">
+        <v>242</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>4383</v>
+      </c>
+      <c r="N27" t="n">
+        <v>111</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>68962</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>38936</v>
+      </c>
+      <c r="R27" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S27" t="n">
+        <v>16550</v>
+      </c>
+      <c r="T27" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U27" t="n">
+        <v>5627</v>
+      </c>
+      <c r="V27" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="X27" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD27"/>
+  <dimension ref="A1:AD28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3041,6 +3041,101 @@
       <c r="AD27" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>15:36:34</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8292</v>
+      </c>
+      <c r="F28" t="n">
+        <v>40810</v>
+      </c>
+      <c r="G28" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.778</v>
+      </c>
+      <c r="I28" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J28" t="n">
+        <v>5963</v>
+      </c>
+      <c r="K28" t="n">
+        <v>138</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>4431</v>
+      </c>
+      <c r="N28" t="n">
+        <v>48</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>69383</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>39024</v>
+      </c>
+      <c r="R28" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S28" t="n">
+        <v>16470</v>
+      </c>
+      <c r="T28" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U28" t="n">
+        <v>5621</v>
+      </c>
+      <c r="V28" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="X28" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD28"/>
+  <dimension ref="A1:AD29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3134,6 +3134,101 @@
         </is>
       </c>
       <c r="AD28" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>15:37:39</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8293</v>
+      </c>
+      <c r="F29" t="n">
+        <v>40862</v>
+      </c>
+      <c r="G29" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.786</v>
+      </c>
+      <c r="I29" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J29" t="n">
+        <v>5967</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>4498</v>
+      </c>
+      <c r="N29" t="n">
+        <v>67</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>69704</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>39023</v>
+      </c>
+      <c r="R29" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S29" t="n">
+        <v>16490</v>
+      </c>
+      <c r="T29" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U29" t="n">
+        <v>5615</v>
+      </c>
+      <c r="V29" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="X29" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
         <is>
           <t>⚠ Conflict</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD29"/>
+  <dimension ref="A1:AD30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3229,6 +3229,101 @@
         </is>
       </c>
       <c r="AD29" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>15:38:46</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E30" t="n">
+        <v>8298</v>
+      </c>
+      <c r="F30" t="n">
+        <v>40995</v>
+      </c>
+      <c r="G30" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.797</v>
+      </c>
+      <c r="I30" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J30" t="n">
+        <v>6143</v>
+      </c>
+      <c r="K30" t="n">
+        <v>176</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>4583</v>
+      </c>
+      <c r="N30" t="n">
+        <v>85</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>70513</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>39250</v>
+      </c>
+      <c r="R30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S30" t="n">
+        <v>16495</v>
+      </c>
+      <c r="T30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U30" t="n">
+        <v>5618</v>
+      </c>
+      <c r="V30" t="n">
+        <v>50.5</v>
+      </c>
+      <c r="X30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
         <is>
           <t>⚠ Conflict</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD30"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3324,6 +3324,101 @@
         </is>
       </c>
       <c r="AD30" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>15:39:51</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="E31" t="n">
+        <v>8302</v>
+      </c>
+      <c r="F31" t="n">
+        <v>41069</v>
+      </c>
+      <c r="G31" t="n">
+        <v>14.68</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.779</v>
+      </c>
+      <c r="I31" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J31" t="n">
+        <v>6309</v>
+      </c>
+      <c r="K31" t="n">
+        <v>166</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>4863</v>
+      </c>
+      <c r="N31" t="n">
+        <v>280</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>70680</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>39728</v>
+      </c>
+      <c r="R31" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S31" t="n">
+        <v>16475</v>
+      </c>
+      <c r="T31" t="n">
+        <v>8000</v>
+      </c>
+      <c r="U31" t="n">
+        <v>5616</v>
+      </c>
+      <c r="V31" t="n">
+        <v>50.3</v>
+      </c>
+      <c r="X31" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>8200</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Bullish (Strong)</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
         <is>
           <t>⚠ Conflict</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD31"/>
+  <dimension ref="A1:AD32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3421,6 +3421,95 @@
       <c r="AD31" t="inlineStr">
         <is>
           <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20:02:10</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E32" t="n">
+        <v>8255</v>
+      </c>
+      <c r="F32" t="n">
+        <v>42781</v>
+      </c>
+      <c r="G32" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.553</v>
+      </c>
+      <c r="I32" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J32" t="n">
+        <v>6453</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>3268</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>87370</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>56257</v>
+      </c>
+      <c r="R32" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S32" t="n">
+        <v>16861</v>
+      </c>
+      <c r="T32" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U32" t="n">
+        <v>9975</v>
+      </c>
+      <c r="V32" t="n">
+        <v>49</v>
+      </c>
+      <c r="X32" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD32"/>
+  <dimension ref="A1:AD33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3508,6 +3508,101 @@
         </is>
       </c>
       <c r="AD32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20:03:11</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8254</v>
+      </c>
+      <c r="F33" t="n">
+        <v>42814</v>
+      </c>
+      <c r="G33" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="I33" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J33" t="n">
+        <v>6379</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-74</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>3254</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-14</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>86808</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>56160</v>
+      </c>
+      <c r="R33" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S33" t="n">
+        <v>16615</v>
+      </c>
+      <c r="T33" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U33" t="n">
+        <v>9873</v>
+      </c>
+      <c r="V33" t="n">
+        <v>49</v>
+      </c>
+      <c r="X33" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD33"/>
+  <dimension ref="A1:AD34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3603,6 +3603,101 @@
         </is>
       </c>
       <c r="AD33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20:04:12</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E34" t="n">
+        <v>8253</v>
+      </c>
+      <c r="F34" t="n">
+        <v>42829</v>
+      </c>
+      <c r="G34" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.538</v>
+      </c>
+      <c r="I34" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J34" t="n">
+        <v>6387</v>
+      </c>
+      <c r="K34" t="n">
+        <v>8</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>3342</v>
+      </c>
+      <c r="N34" t="n">
+        <v>88</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>86789</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>56415</v>
+      </c>
+      <c r="R34" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S34" t="n">
+        <v>16615</v>
+      </c>
+      <c r="T34" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U34" t="n">
+        <v>9961</v>
+      </c>
+      <c r="V34" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="X34" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD34"/>
+  <dimension ref="A1:AD35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3698,6 +3698,101 @@
         </is>
       </c>
       <c r="AD34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20:05:13</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E35" t="n">
+        <v>8255</v>
+      </c>
+      <c r="F35" t="n">
+        <v>42745</v>
+      </c>
+      <c r="G35" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.537</v>
+      </c>
+      <c r="I35" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J35" t="n">
+        <v>6437</v>
+      </c>
+      <c r="K35" t="n">
+        <v>50</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>3414</v>
+      </c>
+      <c r="N35" t="n">
+        <v>72</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>86853</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>56514</v>
+      </c>
+      <c r="R35" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S35" t="n">
+        <v>16604</v>
+      </c>
+      <c r="T35" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U35" t="n">
+        <v>10002</v>
+      </c>
+      <c r="V35" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="X35" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD35"/>
+  <dimension ref="A1:AD36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3795,6 +3795,101 @@
       <c r="AD35" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20:06:14</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E36" t="n">
+        <v>8248</v>
+      </c>
+      <c r="F36" t="n">
+        <v>42781</v>
+      </c>
+      <c r="G36" t="n">
+        <v>19.46</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.531</v>
+      </c>
+      <c r="I36" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J36" t="n">
+        <v>6439</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>3468</v>
+      </c>
+      <c r="N36" t="n">
+        <v>54</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>86885</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>56761</v>
+      </c>
+      <c r="R36" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S36" t="n">
+        <v>16609</v>
+      </c>
+      <c r="T36" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U36" t="n">
+        <v>10156</v>
+      </c>
+      <c r="V36" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="X36" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD36"/>
+  <dimension ref="A1:AD37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3888,6 +3888,101 @@
         </is>
       </c>
       <c r="AD36" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20:07:15</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E37" t="n">
+        <v>8247</v>
+      </c>
+      <c r="F37" t="n">
+        <v>42753</v>
+      </c>
+      <c r="G37" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.535</v>
+      </c>
+      <c r="I37" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J37" t="n">
+        <v>6638</v>
+      </c>
+      <c r="K37" t="n">
+        <v>199</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>3565</v>
+      </c>
+      <c r="N37" t="n">
+        <v>97</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>87071</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>56730</v>
+      </c>
+      <c r="R37" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S37" t="n">
+        <v>16628</v>
+      </c>
+      <c r="T37" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U37" t="n">
+        <v>10195</v>
+      </c>
+      <c r="V37" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="X37" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
         <is>
           <t>⚠ Conflict</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD37"/>
+  <dimension ref="A1:AD38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3983,6 +3983,101 @@
         </is>
       </c>
       <c r="AD37" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>20:08:16</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>8243</v>
+      </c>
+      <c r="F38" t="n">
+        <v>42771</v>
+      </c>
+      <c r="G38" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.539</v>
+      </c>
+      <c r="I38" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J38" t="n">
+        <v>6794</v>
+      </c>
+      <c r="K38" t="n">
+        <v>156</v>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M38" t="n">
+        <v>3630</v>
+      </c>
+      <c r="N38" t="n">
+        <v>65</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P38" t="n">
+        <v>87251</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>56711</v>
+      </c>
+      <c r="R38" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S38" t="n">
+        <v>16676</v>
+      </c>
+      <c r="T38" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U38" t="n">
+        <v>10172</v>
+      </c>
+      <c r="V38" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="X38" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
         <is>
           <t>⚠ Conflict</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD38"/>
+  <dimension ref="A1:AD39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4078,6 +4078,101 @@
         </is>
       </c>
       <c r="AD38" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>20:09:18</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E39" t="n">
+        <v>8246</v>
+      </c>
+      <c r="F39" t="n">
+        <v>42794</v>
+      </c>
+      <c r="G39" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.539</v>
+      </c>
+      <c r="I39" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J39" t="n">
+        <v>6774</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-20</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>3665</v>
+      </c>
+      <c r="N39" t="n">
+        <v>35</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P39" t="n">
+        <v>87256</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>56714</v>
+      </c>
+      <c r="R39" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S39" t="n">
+        <v>16728</v>
+      </c>
+      <c r="T39" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U39" t="n">
+        <v>10082</v>
+      </c>
+      <c r="V39" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="X39" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
         <is>
           <t>⚠ Conflict</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD39"/>
+  <dimension ref="A1:AD40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4173,6 +4173,101 @@
         </is>
       </c>
       <c r="AD39" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>20:10:19</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>8243</v>
+      </c>
+      <c r="F40" t="n">
+        <v>42699</v>
+      </c>
+      <c r="G40" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.543</v>
+      </c>
+      <c r="I40" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J40" t="n">
+        <v>6809</v>
+      </c>
+      <c r="K40" t="n">
+        <v>35</v>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M40" t="n">
+        <v>3554</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-111</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>87139</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>56475</v>
+      </c>
+      <c r="R40" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S40" t="n">
+        <v>16702</v>
+      </c>
+      <c r="T40" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U40" t="n">
+        <v>10057</v>
+      </c>
+      <c r="V40" t="n">
+        <v>49</v>
+      </c>
+      <c r="X40" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
         <is>
           <t>⚠ Conflict</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD40"/>
+  <dimension ref="A1:AD41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4268,6 +4268,101 @@
         </is>
       </c>
       <c r="AD40" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>20:11:20</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E41" t="n">
+        <v>8245</v>
+      </c>
+      <c r="F41" t="n">
+        <v>42733</v>
+      </c>
+      <c r="G41" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.548</v>
+      </c>
+      <c r="I41" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J41" t="n">
+        <v>6839</v>
+      </c>
+      <c r="K41" t="n">
+        <v>30</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>3524</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-30</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
+        <v>87134</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>56299</v>
+      </c>
+      <c r="R41" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S41" t="n">
+        <v>16575</v>
+      </c>
+      <c r="T41" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U41" t="n">
+        <v>9885</v>
+      </c>
+      <c r="V41" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="X41" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
         <is>
           <t>⚠ Conflict</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD41"/>
+  <dimension ref="A1:AD42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4365,6 +4365,101 @@
       <c r="AD41" t="inlineStr">
         <is>
           <t>⚠ Conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>20:12:21</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E42" t="n">
+        <v>8263</v>
+      </c>
+      <c r="F42" t="n">
+        <v>42751</v>
+      </c>
+      <c r="G42" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="H42" t="n">
+        <v>1.551</v>
+      </c>
+      <c r="I42" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J42" t="n">
+        <v>6727</v>
+      </c>
+      <c r="K42" t="n">
+        <v>-112</v>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M42" t="n">
+        <v>3353</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-171</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>86844</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>55997</v>
+      </c>
+      <c r="R42" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S42" t="n">
+        <v>16557</v>
+      </c>
+      <c r="T42" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U42" t="n">
+        <v>9819</v>
+      </c>
+      <c r="V42" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="X42" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD42"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4458,6 +4458,101 @@
         </is>
       </c>
       <c r="AD42" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>20:13:22</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E43" t="n">
+        <v>8264</v>
+      </c>
+      <c r="F43" t="n">
+        <v>42759</v>
+      </c>
+      <c r="G43" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.549</v>
+      </c>
+      <c r="I43" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J43" t="n">
+        <v>6628</v>
+      </c>
+      <c r="K43" t="n">
+        <v>-99</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>3333</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-20</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>86502</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>55833</v>
+      </c>
+      <c r="R43" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S43" t="n">
+        <v>16493</v>
+      </c>
+      <c r="T43" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U43" t="n">
+        <v>9853</v>
+      </c>
+      <c r="V43" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="X43" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD43" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD43"/>
+  <dimension ref="A1:AD44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4555,6 +4555,101 @@
       <c r="AD43" t="inlineStr">
         <is>
           <t>✓ Confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>20:14:23</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E44" t="n">
+        <v>8257</v>
+      </c>
+      <c r="F44" t="n">
+        <v>42773</v>
+      </c>
+      <c r="G44" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.543</v>
+      </c>
+      <c r="I44" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J44" t="n">
+        <v>6623</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M44" t="n">
+        <v>3291</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-42</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>86396</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>55986</v>
+      </c>
+      <c r="R44" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S44" t="n">
+        <v>16465</v>
+      </c>
+      <c r="T44" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U44" t="n">
+        <v>10006</v>
+      </c>
+      <c r="V44" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="X44" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD44"/>
+  <dimension ref="A1:AD45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4648,6 +4648,101 @@
         </is>
       </c>
       <c r="AD44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>20:15:24</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E45" t="n">
+        <v>8255</v>
+      </c>
+      <c r="F45" t="n">
+        <v>42793</v>
+      </c>
+      <c r="G45" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.539</v>
+      </c>
+      <c r="I45" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J45" t="n">
+        <v>6583</v>
+      </c>
+      <c r="K45" t="n">
+        <v>-40</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>3339</v>
+      </c>
+      <c r="N45" t="n">
+        <v>48</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>86331</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>56100</v>
+      </c>
+      <c r="R45" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S45" t="n">
+        <v>16454</v>
+      </c>
+      <c r="T45" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U45" t="n">
+        <v>9984</v>
+      </c>
+      <c r="V45" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="X45" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD45" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH2"/>
+  <dimension ref="A1:AH3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,6 +704,121 @@
         </is>
       </c>
       <c r="AH2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20:17:07</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E3" t="n">
+        <v>8257</v>
+      </c>
+      <c r="F3" t="n">
+        <v>42784</v>
+      </c>
+      <c r="G3" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.539</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6624</v>
+      </c>
+      <c r="K3" t="n">
+        <v>31</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>3366</v>
+      </c>
+      <c r="N3" t="n">
+        <v>69</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P3" t="n">
+        <v>86307</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>56079</v>
+      </c>
+      <c r="R3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>16455</v>
+      </c>
+      <c r="T3" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U3" t="n">
+        <v>10098</v>
+      </c>
+      <c r="V3" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="X3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AH4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,6 +819,121 @@
         </is>
       </c>
       <c r="AH3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20:18:08</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8255</v>
+      </c>
+      <c r="F4" t="n">
+        <v>42753</v>
+      </c>
+      <c r="G4" t="n">
+        <v>19.38</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.536</v>
+      </c>
+      <c r="I4" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J4" t="n">
+        <v>6583</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-41</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>3335</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-31</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P4" t="n">
+        <v>86081</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>56042</v>
+      </c>
+      <c r="R4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S4" t="n">
+        <v>16435</v>
+      </c>
+      <c r="T4" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U4" t="n">
+        <v>10093</v>
+      </c>
+      <c r="V4" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="X4" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH4"/>
+  <dimension ref="A1:AH5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -936,6 +936,121 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20:19:09</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E5" t="n">
+        <v>8265</v>
+      </c>
+      <c r="F5" t="n">
+        <v>42907</v>
+      </c>
+      <c r="G5" t="n">
+        <v>19.81</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.544</v>
+      </c>
+      <c r="I5" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6666</v>
+      </c>
+      <c r="K5" t="n">
+        <v>83</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>3373</v>
+      </c>
+      <c r="N5" t="n">
+        <v>38</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P5" t="n">
+        <v>86252</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>55852</v>
+      </c>
+      <c r="R5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>16435</v>
+      </c>
+      <c r="T5" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U5" t="n">
+        <v>10026</v>
+      </c>
+      <c r="V5" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="X5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>4/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH5"/>
+  <dimension ref="A1:AH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1049,6 +1049,121 @@
         </is>
       </c>
       <c r="AH5" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20:20:10</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="E6" t="n">
+        <v>8269</v>
+      </c>
+      <c r="F6" t="n">
+        <v>42886</v>
+      </c>
+      <c r="G6" t="n">
+        <v>19.75</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.546</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6715</v>
+      </c>
+      <c r="K6" t="n">
+        <v>49</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>3313</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-60</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P6" t="n">
+        <v>86175</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>55758</v>
+      </c>
+      <c r="R6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>16434</v>
+      </c>
+      <c r="T6" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U6" t="n">
+        <v>9968</v>
+      </c>
+      <c r="V6" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="X6" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH6"/>
+  <dimension ref="A1:AH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1164,6 +1164,121 @@
         </is>
       </c>
       <c r="AH6" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20:21:11</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8264</v>
+      </c>
+      <c r="F7" t="n">
+        <v>42866</v>
+      </c>
+      <c r="G7" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.535</v>
+      </c>
+      <c r="I7" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6558</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-157</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>3408</v>
+      </c>
+      <c r="N7" t="n">
+        <v>95</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
+        <v>85751</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>55871</v>
+      </c>
+      <c r="R7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S7" t="n">
+        <v>16430</v>
+      </c>
+      <c r="T7" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U7" t="n">
+        <v>9954</v>
+      </c>
+      <c r="V7" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="X7" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH7"/>
+  <dimension ref="A1:AH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1279,6 +1279,121 @@
         </is>
       </c>
       <c r="AH7" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20:22:12</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8270</v>
+      </c>
+      <c r="F8" t="n">
+        <v>42842</v>
+      </c>
+      <c r="G8" t="n">
+        <v>19.63</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.542</v>
+      </c>
+      <c r="I8" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6545</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-13</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>3430</v>
+      </c>
+      <c r="N8" t="n">
+        <v>22</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>85582</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>55485</v>
+      </c>
+      <c r="R8" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S8" t="n">
+        <v>16405</v>
+      </c>
+      <c r="T8" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U8" t="n">
+        <v>10022</v>
+      </c>
+      <c r="V8" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="X8" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>4/4</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH8"/>
+  <dimension ref="A1:AH9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1396,6 +1396,121 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>20:23:14</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8264</v>
+      </c>
+      <c r="F9" t="n">
+        <v>42834</v>
+      </c>
+      <c r="G9" t="n">
+        <v>19.61</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.532</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J9" t="n">
+        <v>6498</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-47</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>3497</v>
+      </c>
+      <c r="N9" t="n">
+        <v>67</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>85432</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>55779</v>
+      </c>
+      <c r="R9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S9" t="n">
+        <v>16388</v>
+      </c>
+      <c r="T9" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U9" t="n">
+        <v>10127</v>
+      </c>
+      <c r="V9" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="X9" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>3/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH9"/>
+  <dimension ref="A1:AH10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1511,6 +1511,121 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>3/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>20:24:15</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E10" t="n">
+        <v>8257</v>
+      </c>
+      <c r="F10" t="n">
+        <v>42775</v>
+      </c>
+      <c r="G10" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J10" t="n">
+        <v>6493</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>3578</v>
+      </c>
+      <c r="N10" t="n">
+        <v>81</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>85296</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>56125</v>
+      </c>
+      <c r="R10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S10" t="n">
+        <v>16381</v>
+      </c>
+      <c r="T10" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U10" t="n">
+        <v>10299</v>
+      </c>
+      <c r="V10" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="X10" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0/1</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH10"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1624,6 +1624,121 @@
         </is>
       </c>
       <c r="AH10" t="inlineStr">
+        <is>
+          <t>0/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>20:25:16</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E11" t="n">
+        <v>8255</v>
+      </c>
+      <c r="F11" t="n">
+        <v>42746</v>
+      </c>
+      <c r="G11" t="n">
+        <v>19.36</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.518</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6496</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>3651</v>
+      </c>
+      <c r="N11" t="n">
+        <v>73</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>85228</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>56149</v>
+      </c>
+      <c r="R11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S11" t="n">
+        <v>16415</v>
+      </c>
+      <c r="T11" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U11" t="n">
+        <v>10307</v>
+      </c>
+      <c r="V11" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
         <is>
           <t>0/1</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH11"/>
+  <dimension ref="A1:AH12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1741,6 +1741,121 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>0/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20:26:17</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8248</v>
+      </c>
+      <c r="F12" t="n">
+        <v>42710</v>
+      </c>
+      <c r="G12" t="n">
+        <v>19.26</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I12" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J12" t="n">
+        <v>6581</v>
+      </c>
+      <c r="K12" t="n">
+        <v>85</v>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>3827</v>
+      </c>
+      <c r="N12" t="n">
+        <v>176</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>85050</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>56316</v>
+      </c>
+      <c r="R12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>16380</v>
+      </c>
+      <c r="T12" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U12" t="n">
+        <v>10358</v>
+      </c>
+      <c r="V12" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="X12" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH12"/>
+  <dimension ref="A1:AH13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1854,6 +1854,121 @@
         </is>
       </c>
       <c r="AH12" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>20:27:18</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E13" t="n">
+        <v>8252</v>
+      </c>
+      <c r="F13" t="n">
+        <v>42725</v>
+      </c>
+      <c r="G13" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="I13" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6539</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-42</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>3733</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-94</v>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>85118</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>56344</v>
+      </c>
+      <c r="R13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>16358</v>
+      </c>
+      <c r="T13" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U13" t="n">
+        <v>10362</v>
+      </c>
+      <c r="V13" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="X13" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH13"/>
+  <dimension ref="A1:AH14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1969,6 +1969,121 @@
         </is>
       </c>
       <c r="AH13" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20:28:19</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E14" t="n">
+        <v>8248</v>
+      </c>
+      <c r="F14" t="n">
+        <v>42756</v>
+      </c>
+      <c r="G14" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="I14" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J14" t="n">
+        <v>6655</v>
+      </c>
+      <c r="K14" t="n">
+        <v>116</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>3765</v>
+      </c>
+      <c r="N14" t="n">
+        <v>32</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>84964</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>56485</v>
+      </c>
+      <c r="R14" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>16321</v>
+      </c>
+      <c r="T14" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U14" t="n">
+        <v>10369</v>
+      </c>
+      <c r="V14" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="X14" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH14"/>
+  <dimension ref="A1:AH15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2084,6 +2084,121 @@
         </is>
       </c>
       <c r="AH14" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20:29:20</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E15" t="n">
+        <v>8246</v>
+      </c>
+      <c r="F15" t="n">
+        <v>42655</v>
+      </c>
+      <c r="G15" t="n">
+        <v>19.11</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.502</v>
+      </c>
+      <c r="I15" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J15" t="n">
+        <v>6697</v>
+      </c>
+      <c r="K15" t="n">
+        <v>42</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>3842</v>
+      </c>
+      <c r="N15" t="n">
+        <v>77</v>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>85011</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>56580</v>
+      </c>
+      <c r="R15" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>16281</v>
+      </c>
+      <c r="T15" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U15" t="n">
+        <v>10463</v>
+      </c>
+      <c r="V15" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="X15" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH15"/>
+  <dimension ref="A1:AH16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2201,6 +2201,121 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>20:30:21</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E16" t="n">
+        <v>8255</v>
+      </c>
+      <c r="F16" t="n">
+        <v>42625</v>
+      </c>
+      <c r="G16" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.493</v>
+      </c>
+      <c r="I16" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J16" t="n">
+        <v>6708</v>
+      </c>
+      <c r="K16" t="n">
+        <v>11</v>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>3885</v>
+      </c>
+      <c r="N16" t="n">
+        <v>43</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>84564</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>56652</v>
+      </c>
+      <c r="R16" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>16113</v>
+      </c>
+      <c r="T16" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U16" t="n">
+        <v>10455</v>
+      </c>
+      <c r="V16" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="X16" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>1/1</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH16"/>
+  <dimension ref="A1:AH17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2316,6 +2316,121 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>20:31:22</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8255</v>
+      </c>
+      <c r="F17" t="n">
+        <v>42623</v>
+      </c>
+      <c r="G17" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.496</v>
+      </c>
+      <c r="I17" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6750</v>
+      </c>
+      <c r="K17" t="n">
+        <v>42</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>3901</v>
+      </c>
+      <c r="N17" t="n">
+        <v>16</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>84715</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>56642</v>
+      </c>
+      <c r="R17" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>16130</v>
+      </c>
+      <c r="T17" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U17" t="n">
+        <v>10434</v>
+      </c>
+      <c r="V17" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="X17" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH17"/>
+  <dimension ref="A1:AH18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2431,6 +2431,121 @@
       <c r="AH17" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>20:32:23</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8255</v>
+      </c>
+      <c r="F18" t="n">
+        <v>42581</v>
+      </c>
+      <c r="G18" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.493</v>
+      </c>
+      <c r="I18" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6832</v>
+      </c>
+      <c r="K18" t="n">
+        <v>82</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>3919</v>
+      </c>
+      <c r="N18" t="n">
+        <v>18</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>84658</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>56696</v>
+      </c>
+      <c r="R18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>16147</v>
+      </c>
+      <c r="T18" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U18" t="n">
+        <v>10452</v>
+      </c>
+      <c r="V18" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="X18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>1/1</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH18"/>
+  <dimension ref="A1:AH19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2546,6 +2546,121 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>20:33:24</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E19" t="n">
+        <v>8260</v>
+      </c>
+      <c r="F19" t="n">
+        <v>42721</v>
+      </c>
+      <c r="G19" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.486</v>
+      </c>
+      <c r="I19" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J19" t="n">
+        <v>6844</v>
+      </c>
+      <c r="K19" t="n">
+        <v>12</v>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M19" t="n">
+        <v>3905</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-14</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>84639</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>56963</v>
+      </c>
+      <c r="R19" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S19" t="n">
+        <v>16145</v>
+      </c>
+      <c r="T19" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U19" t="n">
+        <v>10597</v>
+      </c>
+      <c r="V19" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="X19" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>1/2</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH19"/>
+  <dimension ref="A1:AH20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2661,6 +2661,121 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>1/2</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>20:34:25</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E20" t="n">
+        <v>8258</v>
+      </c>
+      <c r="F20" t="n">
+        <v>42727</v>
+      </c>
+      <c r="G20" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.474</v>
+      </c>
+      <c r="I20" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6844</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>3896</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-9</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>84652</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>57441</v>
+      </c>
+      <c r="R20" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S20" t="n">
+        <v>16145</v>
+      </c>
+      <c r="T20" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U20" t="n">
+        <v>10928</v>
+      </c>
+      <c r="V20" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="X20" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>0/1</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH20"/>
+  <dimension ref="A1:AH21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2776,6 +2776,121 @@
       <c r="AH20" t="inlineStr">
         <is>
           <t>0/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>20:35:26</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>8267</v>
+      </c>
+      <c r="F21" t="n">
+        <v>42719</v>
+      </c>
+      <c r="G21" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.482</v>
+      </c>
+      <c r="I21" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6800</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-44</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>3918</v>
+      </c>
+      <c r="N21" t="n">
+        <v>22</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>84945</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>57322</v>
+      </c>
+      <c r="R21" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S21" t="n">
+        <v>16363</v>
+      </c>
+      <c r="T21" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U21" t="n">
+        <v>10894</v>
+      </c>
+      <c r="V21" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="X21" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>3/3</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH21"/>
+  <dimension ref="A1:AH22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2889,6 +2889,121 @@
         </is>
       </c>
       <c r="AH21" t="inlineStr">
+        <is>
+          <t>3/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>20:36:27</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E22" t="n">
+        <v>8274</v>
+      </c>
+      <c r="F22" t="n">
+        <v>42739</v>
+      </c>
+      <c r="G22" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.473</v>
+      </c>
+      <c r="I22" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6800</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Flat</t>
+        </is>
+      </c>
+      <c r="M22" t="n">
+        <v>3974</v>
+      </c>
+      <c r="N22" t="n">
+        <v>56</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>84858</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>57617</v>
+      </c>
+      <c r="R22" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S22" t="n">
+        <v>16352</v>
+      </c>
+      <c r="T22" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U22" t="n">
+        <v>10989</v>
+      </c>
+      <c r="V22" t="n">
+        <v>49.1</v>
+      </c>
+      <c r="X22" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
         <is>
           <t>3/3</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH22"/>
+  <dimension ref="A1:AH24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3006,6 +3006,230 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>3/3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>20:37:29</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E23" t="n">
+        <v>8275</v>
+      </c>
+      <c r="F23" t="n">
+        <v>42735</v>
+      </c>
+      <c r="G23" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.431</v>
+      </c>
+      <c r="I23" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J23" t="n">
+        <v>10350</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3550</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>11177</v>
+      </c>
+      <c r="N23" t="n">
+        <v>7203</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>84263</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>58896</v>
+      </c>
+      <c r="R23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S23" t="n">
+        <v>16352</v>
+      </c>
+      <c r="T23" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U23" t="n">
+        <v>11177</v>
+      </c>
+      <c r="V23" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="X23" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>4/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>20:37:32</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E24" t="n">
+        <v>8277</v>
+      </c>
+      <c r="F24" t="n">
+        <v>42737</v>
+      </c>
+      <c r="G24" t="n">
+        <v>19.34</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I24" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J24" t="n">
+        <v>10350</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>11193</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P24" t="n">
+        <v>84263</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>58906</v>
+      </c>
+      <c r="R24" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S24" t="n">
+        <v>16352</v>
+      </c>
+      <c r="T24" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U24" t="n">
+        <v>11193</v>
+      </c>
+      <c r="V24" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="X24" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH24"/>
+  <dimension ref="A1:AH25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3228,6 +3228,121 @@
         </is>
       </c>
       <c r="AH24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>20:38:34</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8275</v>
+      </c>
+      <c r="F25" t="n">
+        <v>42729</v>
+      </c>
+      <c r="G25" t="n">
+        <v>19.31</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.474</v>
+      </c>
+      <c r="I25" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J25" t="n">
+        <v>6806</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-3544</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M25" t="n">
+        <v>3952</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-7241</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P25" t="n">
+        <v>84910</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>57607</v>
+      </c>
+      <c r="R25" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S25" t="n">
+        <v>16444</v>
+      </c>
+      <c r="T25" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U25" t="n">
+        <v>11193</v>
+      </c>
+      <c r="V25" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="X25" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH25"/>
+  <dimension ref="A1:AH26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3345,6 +3345,121 @@
       <c r="AH25" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20:39:35</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="E26" t="n">
+        <v>8268</v>
+      </c>
+      <c r="F26" t="n">
+        <v>42724</v>
+      </c>
+      <c r="G26" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.491</v>
+      </c>
+      <c r="I26" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J26" t="n">
+        <v>6753</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-53</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M26" t="n">
+        <v>3757</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-195</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P26" t="n">
+        <v>84763</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>56841</v>
+      </c>
+      <c r="R26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S26" t="n">
+        <v>16562</v>
+      </c>
+      <c r="T26" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U26" t="n">
+        <v>10981</v>
+      </c>
+      <c r="V26" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="X26" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>0/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH26"/>
+  <dimension ref="A1:AH27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3458,6 +3458,121 @@
         </is>
       </c>
       <c r="AH26" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20:40:36</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E27" t="n">
+        <v>8248</v>
+      </c>
+      <c r="F27" t="n">
+        <v>42712</v>
+      </c>
+      <c r="G27" t="n">
+        <v>19.27</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.492</v>
+      </c>
+      <c r="I27" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J27" t="n">
+        <v>6796</v>
+      </c>
+      <c r="K27" t="n">
+        <v>43</v>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>3784</v>
+      </c>
+      <c r="N27" t="n">
+        <v>27</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P27" t="n">
+        <v>84652</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>56726</v>
+      </c>
+      <c r="R27" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S27" t="n">
+        <v>16582</v>
+      </c>
+      <c r="T27" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U27" t="n">
+        <v>10934</v>
+      </c>
+      <c r="V27" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="X27" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH27"/>
+  <dimension ref="A1:AH28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3573,6 +3573,121 @@
         </is>
       </c>
       <c r="AH27" t="inlineStr">
+        <is>
+          <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20:41:37</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="E28" t="n">
+        <v>8272</v>
+      </c>
+      <c r="F28" t="n">
+        <v>42697</v>
+      </c>
+      <c r="G28" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.492</v>
+      </c>
+      <c r="I28" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J28" t="n">
+        <v>6800</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>3787</v>
+      </c>
+      <c r="N28" t="n">
+        <v>3</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P28" t="n">
+        <v>84525</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>56671</v>
+      </c>
+      <c r="R28" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S28" t="n">
+        <v>16603</v>
+      </c>
+      <c r="T28" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U28" t="n">
+        <v>10941</v>
+      </c>
+      <c r="V28" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="X28" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH28" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH28"/>
+  <dimension ref="A1:AH29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3690,6 +3690,121 @@
       <c r="AH28" t="inlineStr">
         <is>
           <t>0/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>20:42:38</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8274</v>
+      </c>
+      <c r="F29" t="n">
+        <v>42730</v>
+      </c>
+      <c r="G29" t="n">
+        <v>19.32</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.493</v>
+      </c>
+      <c r="I29" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J29" t="n">
+        <v>6867</v>
+      </c>
+      <c r="K29" t="n">
+        <v>67</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>3789</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P29" t="n">
+        <v>84598</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>56647</v>
+      </c>
+      <c r="R29" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S29" t="n">
+        <v>16631</v>
+      </c>
+      <c r="T29" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U29" t="n">
+        <v>11012</v>
+      </c>
+      <c r="V29" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="X29" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH29"/>
+  <dimension ref="A1:AH30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3805,6 +3805,121 @@
       <c r="AH29" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>20:43:39</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E30" t="n">
+        <v>8277</v>
+      </c>
+      <c r="F30" t="n">
+        <v>42649</v>
+      </c>
+      <c r="G30" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.444</v>
+      </c>
+      <c r="I30" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J30" t="n">
+        <v>10060</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3193</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>11016</v>
+      </c>
+      <c r="N30" t="n">
+        <v>7227</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P30" t="n">
+        <v>83599</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>57877</v>
+      </c>
+      <c r="R30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S30" t="n">
+        <v>16617</v>
+      </c>
+      <c r="T30" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U30" t="n">
+        <v>11016</v>
+      </c>
+      <c r="V30" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="X30" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>1/1</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH30"/>
+  <dimension ref="A1:AH31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3920,6 +3920,121 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>20:44:40</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E31" t="n">
+        <v>8267</v>
+      </c>
+      <c r="F31" t="n">
+        <v>42666</v>
+      </c>
+      <c r="G31" t="n">
+        <v>19.14</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.483</v>
+      </c>
+      <c r="I31" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J31" t="n">
+        <v>6547</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-3513</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>3821</v>
+      </c>
+      <c r="N31" t="n">
+        <v>-7195</v>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P31" t="n">
+        <v>83910</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>56587</v>
+      </c>
+      <c r="R31" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S31" t="n">
+        <v>16270</v>
+      </c>
+      <c r="T31" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U31" t="n">
+        <v>11044</v>
+      </c>
+      <c r="V31" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="X31" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>⚠ Conflict</t>
+        </is>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>1/4</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH31"/>
+  <dimension ref="A1:AH32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4035,6 +4035,121 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>1/4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>20:45:41</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E32" t="n">
+        <v>8275</v>
+      </c>
+      <c r="F32" t="n">
+        <v>42525</v>
+      </c>
+      <c r="G32" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.452</v>
+      </c>
+      <c r="I32" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J32" t="n">
+        <v>10051</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3504</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>11089</v>
+      </c>
+      <c r="N32" t="n">
+        <v>7268</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P32" t="n">
+        <v>83048</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>57184</v>
+      </c>
+      <c r="R32" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S32" t="n">
+        <v>16011</v>
+      </c>
+      <c r="T32" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U32" t="n">
+        <v>11089</v>
+      </c>
+      <c r="V32" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="X32" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH32"/>
+  <dimension ref="A1:AH33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4148,6 +4148,121 @@
         </is>
       </c>
       <c r="AH32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>20:46:42</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8277</v>
+      </c>
+      <c r="F33" t="n">
+        <v>42495</v>
+      </c>
+      <c r="G33" t="n">
+        <v>18.66</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.462</v>
+      </c>
+      <c r="I33" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J33" t="n">
+        <v>10032</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-19</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>10815</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-274</v>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P33" t="n">
+        <v>83122</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>56867</v>
+      </c>
+      <c r="R33" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S33" t="n">
+        <v>16008</v>
+      </c>
+      <c r="T33" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U33" t="n">
+        <v>10815</v>
+      </c>
+      <c r="V33" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="X33" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH33" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH33"/>
+  <dimension ref="A1:AH34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4263,6 +4263,121 @@
         </is>
       </c>
       <c r="AH33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>20:47:43</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="E34" t="n">
+        <v>8277</v>
+      </c>
+      <c r="F34" t="n">
+        <v>42505</v>
+      </c>
+      <c r="G34" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1.466</v>
+      </c>
+      <c r="I34" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J34" t="n">
+        <v>10054</v>
+      </c>
+      <c r="K34" t="n">
+        <v>22</v>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M34" t="n">
+        <v>10792</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-23</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P34" t="n">
+        <v>83116</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>56706</v>
+      </c>
+      <c r="R34" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S34" t="n">
+        <v>16008</v>
+      </c>
+      <c r="T34" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U34" t="n">
+        <v>10792</v>
+      </c>
+      <c r="V34" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="X34" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH34" t="inlineStr">
         <is>
           <t>—</t>
         </is>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH34"/>
+  <dimension ref="A1:AH35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4380,6 +4380,121 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>20:48:45</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E35" t="n">
+        <v>8280</v>
+      </c>
+      <c r="F35" t="n">
+        <v>42499</v>
+      </c>
+      <c r="G35" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="H35" t="n">
+        <v>1.466</v>
+      </c>
+      <c r="I35" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J35" t="n">
+        <v>10056</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>10801</v>
+      </c>
+      <c r="N35" t="n">
+        <v>9</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P35" t="n">
+        <v>82966</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>56576</v>
+      </c>
+      <c r="R35" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S35" t="n">
+        <v>15959</v>
+      </c>
+      <c r="T35" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U35" t="n">
+        <v>10801</v>
+      </c>
+      <c r="V35" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="X35" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>✓ Confirmed</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>1/1</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH35"/>
+  <dimension ref="A1:AH36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4495,6 +4495,121 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>1/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>20:49:46</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E36" t="n">
+        <v>8275</v>
+      </c>
+      <c r="F36" t="n">
+        <v>42512</v>
+      </c>
+      <c r="G36" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.511</v>
+      </c>
+      <c r="I36" t="n">
+        <v>8250</v>
+      </c>
+      <c r="J36" t="n">
+        <v>6846</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-3210</v>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="M36" t="n">
+        <v>3633</v>
+      </c>
+      <c r="N36" t="n">
+        <v>-7168</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Unwinding</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>83634</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>55354</v>
+      </c>
+      <c r="R36" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S36" t="n">
+        <v>15970</v>
+      </c>
+      <c r="T36" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U36" t="n">
+        <v>10847</v>
+      </c>
+      <c r="V36" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="X36" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
+++ b/backend/signal_logs/2026-08-20/index_tracker_CRUDEOILM_2026-08-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH36"/>
+  <dimension ref="A1:AH37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4608,6 +4608,121 @@
         </is>
       </c>
       <c r="AH36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>20:50:47</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="E37" t="n">
+        <v>8276</v>
+      </c>
+      <c r="F37" t="n">
+        <v>42525</v>
+      </c>
+      <c r="G37" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.471</v>
+      </c>
+      <c r="I37" t="n">
+        <v>8300</v>
+      </c>
+      <c r="J37" t="n">
+        <v>10134</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3288</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>10957</v>
+      </c>
+      <c r="N37" t="n">
+        <v>7324</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Writing</t>
+        </is>
+      </c>
+      <c r="P37" t="n">
+        <v>83332</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>56632</v>
+      </c>
+      <c r="R37" t="n">
+        <v>8000</v>
+      </c>
+      <c r="S37" t="n">
+        <v>15933</v>
+      </c>
+      <c r="T37" t="n">
+        <v>8300</v>
+      </c>
+      <c r="U37" t="n">
+        <v>10957</v>
+      </c>
+      <c r="V37" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="X37" t="n">
+        <v>8000</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>8300</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>8250</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>PE writing dominant (bullish)</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Bullish</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="AH37" t="inlineStr">
         <is>
           <t>—</t>
         </is>
